--- a/uploads/downloadfiles/feesMasterBulkUpload.xlsx
+++ b/uploads/downloadfiles/feesMasterBulkUpload.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="105" windowWidth="27795" windowHeight="12600"/>
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
@@ -45,11 +45,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,7 +170,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,7 +204,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -381,9 +379,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" customWidth="1"/>
@@ -395,7 +393,7 @@
     <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,14 +427,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"Common, Standard Wise"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>"2024-2025,2023-2024"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"New Student, Old Student, Vijayadashami,All[NEW &amp; OLD]"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"PRE.K.G,L.K.G,U.K.G,I,II,III,IV,V,VI,VII,VIII,IX,X,XI_Maths_Biology,XI_Maths_ComputerScience,XI_Biology_ComputerScience,XI_Commerce_ComputerScience,XI_All,XII_Maths_Biology,XII_Maths_ComputerScience,XII_Biology_ComputerScience,XII_Commerce_ComputerScience"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576">
+      <formula1>"         PRE.K.G,L.K.G,U.K.G,I,II,III,IV,V,VI,VII,VIII,IX,X,XI_Maths_Biology,XI_Maths_Csc,XI_Biology_Csc,XI_Commerce_Csc,XI_Com_BusinessMaths,XII_Maths_Biology,XII_Maths_Csc,XII_Biology_Csc,XII_Commerce_Csc,XII_Com_BusinessMaths"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576">
+      <formula1>"2026-2027"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -445,18 +443,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
